--- a/artfynd/A 8562-2025 artfynd.xlsx
+++ b/artfynd/A 8562-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115883100</v>
+        <v>115883525</v>
       </c>
       <c r="B2" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543243</v>
+        <v>543250</v>
       </c>
       <c r="R2" t="n">
-        <v>7234023</v>
+        <v>7234096</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -775,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115883521</v>
+        <v>115883118</v>
       </c>
       <c r="B3" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543257</v>
+        <v>543219</v>
       </c>
       <c r="R3" t="n">
-        <v>7234107</v>
+        <v>7234002</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115883137</v>
+        <v>115883126</v>
       </c>
       <c r="B4" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543335</v>
+        <v>543304</v>
       </c>
       <c r="R4" t="n">
-        <v>7233972</v>
+        <v>7233987</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +971,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115883525</v>
+        <v>115883106</v>
       </c>
       <c r="B5" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543250</v>
+        <v>543204</v>
       </c>
       <c r="R5" t="n">
-        <v>7234096</v>
+        <v>7234016</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1077,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1108,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115883106</v>
+        <v>115883100</v>
       </c>
       <c r="B6" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543204</v>
+        <v>543243</v>
       </c>
       <c r="R6" t="n">
-        <v>7234016</v>
+        <v>7234023</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1230,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115883126</v>
+        <v>115883137</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543304</v>
+        <v>543335</v>
       </c>
       <c r="R7" t="n">
-        <v>7233987</v>
+        <v>7233972</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1319,7 +1289,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1334,117 +1304,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>115883118</v>
-      </c>
-      <c r="B8" t="n">
-        <v>90328</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>543219</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7234002</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
         <is>
           <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>
